--- a/output/laminas_comunales/comunal_m_movinterna_a_2021_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2021_valparaiso.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2020_2021. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2020_2021. Escala comunal recortada a percentiles 3-97.</t>
         </is>
       </c>
     </row>
